--- a/downloads/Th1_pre_post_results.xlsx
+++ b/downloads/Th1_pre_post_results.xlsx
@@ -964,7 +964,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Pre/post designs only</t>
+          <t>Excluding crossover design - Lancaster et al. (2005)</t>
         </is>
       </c>
       <c r="C4">
@@ -1075,7 +1075,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Pre/post designs only</t>
+          <t>Excluding crossover design - Lancaster et al. (2005)</t>
         </is>
       </c>
       <c r="C7">
@@ -1186,7 +1186,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Pre/post designs only</t>
+          <t>Excluding crossover design - Lancaster et al. (2005)</t>
         </is>
       </c>
       <c r="C10">
@@ -1297,7 +1297,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Pre/post designs only</t>
+          <t>Excluding crossover design - Lancaster et al. (2005)</t>
         </is>
       </c>
       <c r="C13">
@@ -1408,7 +1408,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Pre/post designs only</t>
+          <t>Excluding crossover design - Lancaster et al. (2005)</t>
         </is>
       </c>
       <c r="C16">

--- a/downloads/Th1_pre_post_results.xlsx
+++ b/downloads/Th1_pre_post_results.xlsx
@@ -824,7 +824,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:K16"/>
+  <dimension ref="A1:K21"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -997,39 +997,39 @@
     </row>
     <row r="5">
       <c r="A5">
-        <v>0.4</v>
+        <v>0.3</v>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Main analysis</t>
+          <t>Excluding absolute cell counts - Tsubakihara et al. (2012)</t>
         </is>
       </c>
       <c r="C5">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="D5">
-        <v>0.9959744236086967</v>
+        <v>1.079473259512304</v>
       </c>
       <c r="E5">
-        <v>0.450019747246007</v>
+        <v>0.5261971460845767</v>
       </c>
       <c r="F5">
-        <v>1.541929099971386</v>
+        <v>1.632749372940031</v>
       </c>
       <c r="G5">
-        <v>0.001364632816695426</v>
+        <v>0.0008404033737793404</v>
       </c>
       <c r="H5">
-        <v>1.037848208084904</v>
+        <v>0.9687684022031301</v>
       </c>
       <c r="I5">
-        <v>0.8379856592713688</v>
+        <v>0.7762138739543264</v>
       </c>
       <c r="J5">
-        <v>-1.235816199269745</v>
+        <v>-1.095735113972705</v>
       </c>
       <c r="K5">
-        <v>3.227765046487138</v>
+        <v>3.254681632997313</v>
       </c>
     </row>
     <row r="6">
@@ -1038,35 +1038,35 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Lancaster et al. (2005) - n / 3</t>
+          <t>Main analysis</t>
         </is>
       </c>
       <c r="C6">
         <v>17</v>
       </c>
       <c r="D6">
-        <v>1.02279115442236</v>
+        <v>0.9959744236086967</v>
       </c>
       <c r="E6">
-        <v>0.4738916690514067</v>
+        <v>0.450019747246007</v>
       </c>
       <c r="F6">
-        <v>1.571690639793314</v>
+        <v>1.541929099971386</v>
       </c>
       <c r="G6">
-        <v>0.001146187386137065</v>
+        <v>0.001364632816695426</v>
       </c>
       <c r="H6">
-        <v>0.9904068016514798</v>
+        <v>1.037848208084904</v>
       </c>
       <c r="I6">
-        <v>0.8268694819104626</v>
+        <v>0.8379856592713688</v>
       </c>
       <c r="J6">
-        <v>-1.160337105839064</v>
+        <v>-1.235816199269745</v>
       </c>
       <c r="K6">
-        <v>3.205919414683784</v>
+        <v>3.227765046487138</v>
       </c>
     </row>
     <row r="7">
@@ -1075,109 +1075,109 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Excluding crossover design - Lancaster et al. (2005)</t>
+          <t>Lancaster et al. (2005) - n / 3</t>
         </is>
       </c>
       <c r="C7">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="D7">
-        <v>1.173903014580307</v>
+        <v>1.02279115442236</v>
       </c>
       <c r="E7">
-        <v>0.5386199054704532</v>
+        <v>0.4738916690514067</v>
       </c>
       <c r="F7">
-        <v>1.809186123690161</v>
+        <v>1.571690639793314</v>
       </c>
       <c r="G7">
-        <v>0.001534973947760174</v>
+        <v>0.001146187386137065</v>
       </c>
       <c r="H7">
-        <v>1.105487738437113</v>
+        <v>0.9904068016514798</v>
       </c>
       <c r="I7">
-        <v>0.8533280189045062</v>
+        <v>0.8268694819104626</v>
       </c>
       <c r="J7">
-        <v>-1.189069805977938</v>
+        <v>-1.160337105839064</v>
       </c>
       <c r="K7">
-        <v>3.536875835138552</v>
+        <v>3.205919414683784</v>
       </c>
     </row>
     <row r="8">
       <c r="A8">
-        <v>0.5</v>
+        <v>0.4</v>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Main analysis</t>
+          <t>Excluding crossover design - Lancaster et al. (2005)</t>
         </is>
       </c>
       <c r="C8">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="D8">
-        <v>0.9979875900570729</v>
+        <v>1.173903014580307</v>
       </c>
       <c r="E8">
-        <v>0.4523559326796573</v>
+        <v>0.5386199054704532</v>
       </c>
       <c r="F8">
-        <v>1.543619247434489</v>
+        <v>1.809186123690161</v>
       </c>
       <c r="G8">
-        <v>0.001335859620838953</v>
+        <v>0.001534973947760174</v>
       </c>
       <c r="H8">
-        <v>1.053482048396752</v>
+        <v>1.105487738437113</v>
       </c>
       <c r="I8">
-        <v>0.8643591335464124</v>
+        <v>0.8533280189045062</v>
       </c>
       <c r="J8">
-        <v>-1.248830045592003</v>
+        <v>-1.189069805977938</v>
       </c>
       <c r="K8">
-        <v>3.244805225706148</v>
+        <v>3.536875835138552</v>
       </c>
     </row>
     <row r="9">
       <c r="A9">
-        <v>0.5</v>
+        <v>0.4</v>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Lancaster et al. (2005) - n / 3</t>
+          <t>Excluding absolute cell counts - Tsubakihara et al. (2012)</t>
         </is>
       </c>
       <c r="C9">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="D9">
-        <v>1.021224129395345</v>
+        <v>1.08139023472814</v>
       </c>
       <c r="E9">
-        <v>0.4730413736466557</v>
+        <v>0.5275963827993408</v>
       </c>
       <c r="F9">
-        <v>1.569406885144033</v>
+        <v>1.635184086656939</v>
       </c>
       <c r="G9">
-        <v>0.001148349122564616</v>
+        <v>0.0008344907309755415</v>
       </c>
       <c r="H9">
-        <v>1.013990567153034</v>
+        <v>0.9881816872292243</v>
       </c>
       <c r="I9">
-        <v>0.8551145268400544</v>
+        <v>0.8078990451368666</v>
       </c>
       <c r="J9">
-        <v>-1.185483013997614</v>
+        <v>-1.11346118317755</v>
       </c>
       <c r="K9">
-        <v>3.227931272788303</v>
+        <v>3.27624165263383</v>
       </c>
     </row>
     <row r="10">
@@ -1186,151 +1186,151 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Excluding crossover design - Lancaster et al. (2005)</t>
+          <t>Main analysis</t>
         </is>
       </c>
       <c r="C10">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="D10">
-        <v>1.176097424251494</v>
+        <v>0.9979875900570729</v>
       </c>
       <c r="E10">
-        <v>0.5421137325207219</v>
+        <v>0.4523559326796573</v>
       </c>
       <c r="F10">
-        <v>1.810081115982267</v>
+        <v>1.543619247434489</v>
       </c>
       <c r="G10">
-        <v>0.001490373291876303</v>
+        <v>0.001335859620838953</v>
       </c>
       <c r="H10">
-        <v>1.119791157208526</v>
+        <v>1.053482048396752</v>
       </c>
       <c r="I10">
-        <v>0.8772965740415863</v>
+        <v>0.8643591335464124</v>
       </c>
       <c r="J10">
-        <v>-1.200004547899156</v>
+        <v>-1.248830045592003</v>
       </c>
       <c r="K10">
-        <v>3.552199396402144</v>
+        <v>3.244805225706148</v>
       </c>
     </row>
     <row r="11">
       <c r="A11">
-        <v>0.6</v>
+        <v>0.5</v>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Main analysis</t>
+          <t>Lancaster et al. (2005) - n / 3</t>
         </is>
       </c>
       <c r="C11">
         <v>17</v>
       </c>
       <c r="D11">
-        <v>0.9985041158865274</v>
+        <v>1.021224129395345</v>
       </c>
       <c r="E11">
-        <v>0.4540429953223396</v>
+        <v>0.4730413736466557</v>
       </c>
       <c r="F11">
-        <v>1.542965236450715</v>
+        <v>1.569406885144033</v>
       </c>
       <c r="G11">
-        <v>0.001307047392597261</v>
+        <v>0.001148349122564616</v>
       </c>
       <c r="H11">
-        <v>1.065361155259057</v>
+        <v>1.013990567153034</v>
       </c>
       <c r="I11">
-        <v>0.890780135099233</v>
+        <v>0.8551145268400544</v>
       </c>
       <c r="J11">
-        <v>-1.259275461469963</v>
+        <v>-1.185483013997614</v>
       </c>
       <c r="K11">
-        <v>3.256283693243018</v>
+        <v>3.227931272788303</v>
       </c>
     </row>
     <row r="12">
       <c r="A12">
-        <v>0.6</v>
+        <v>0.5</v>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Lancaster et al. (2005) - n / 3</t>
+          <t>Excluding crossover design - Lancaster et al. (2005)</t>
         </is>
       </c>
       <c r="C12">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="D12">
-        <v>1.017891626587008</v>
+        <v>1.176097424251494</v>
       </c>
       <c r="E12">
-        <v>0.471318150203426</v>
+        <v>0.5421137325207219</v>
       </c>
       <c r="F12">
-        <v>1.56446510297059</v>
+        <v>1.810081115982267</v>
       </c>
       <c r="G12">
-        <v>0.001151489383497115</v>
+        <v>0.001490373291876303</v>
       </c>
       <c r="H12">
-        <v>1.03381418460641</v>
+        <v>1.119791157208526</v>
       </c>
       <c r="I12">
-        <v>0.8834093815248419</v>
+        <v>0.8772965740415863</v>
       </c>
       <c r="J12">
-        <v>-1.208099623809543</v>
+        <v>-1.200004547899156</v>
       </c>
       <c r="K12">
-        <v>3.243882876983559</v>
+        <v>3.552199396402144</v>
       </c>
     </row>
     <row r="13">
       <c r="A13">
-        <v>0.6</v>
+        <v>0.5</v>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Excluding crossover design - Lancaster et al. (2005)</t>
+          <t>Excluding absolute cell counts - Tsubakihara et al. (2012)</t>
         </is>
       </c>
       <c r="C13">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="D13">
-        <v>1.17667267981943</v>
+        <v>1.082423693418966</v>
       </c>
       <c r="E13">
-        <v>0.5450977852431191</v>
+        <v>0.5287398421433883</v>
       </c>
       <c r="F13">
-        <v>1.808247574395741</v>
+        <v>1.636107544694544</v>
       </c>
       <c r="G13">
-        <v>0.001442771646569081</v>
+        <v>0.0008264196501024834</v>
       </c>
       <c r="H13">
-        <v>1.129769598097096</v>
+        <v>1.004976822718304</v>
       </c>
       <c r="I13">
-        <v>0.9013060588896876</v>
+        <v>0.8395900190680174</v>
       </c>
       <c r="J13">
-        <v>-1.20793987389064</v>
+        <v>-1.129025942180657</v>
       </c>
       <c r="K13">
-        <v>3.5612852335295</v>
+        <v>3.293873329018589</v>
       </c>
     </row>
     <row r="14">
       <c r="A14">
-        <v>0.7</v>
+        <v>0.6</v>
       </c>
       <c r="B14" t="inlineStr">
         <is>
@@ -1341,33 +1341,33 @@
         <v>17</v>
       </c>
       <c r="D14">
-        <v>0.9961339727332291</v>
+        <v>0.9985041158865274</v>
       </c>
       <c r="E14">
-        <v>0.4541034330686241</v>
+        <v>0.4540429953223396</v>
       </c>
       <c r="F14">
-        <v>1.538164512397834</v>
+        <v>1.542965236450715</v>
       </c>
       <c r="G14">
-        <v>0.001284757590773748</v>
+        <v>0.001307047392597261</v>
       </c>
       <c r="H14">
-        <v>1.071724955611667</v>
+        <v>1.065361155259057</v>
       </c>
       <c r="I14">
-        <v>0.9172857471617978</v>
+        <v>0.890780135099233</v>
       </c>
       <c r="J14">
-        <v>-1.26675486296762</v>
+        <v>-1.259275461469963</v>
       </c>
       <c r="K14">
-        <v>3.259022808434078</v>
+        <v>3.256283693243018</v>
       </c>
     </row>
     <row r="15">
       <c r="A15">
-        <v>0.7</v>
+        <v>0.6</v>
       </c>
       <c r="B15" t="inlineStr">
         <is>
@@ -1378,33 +1378,33 @@
         <v>17</v>
       </c>
       <c r="D15">
-        <v>1.011361691930422</v>
+        <v>1.017891626587008</v>
       </c>
       <c r="E15">
-        <v>0.4676978322482107</v>
+        <v>0.471318150203426</v>
       </c>
       <c r="F15">
-        <v>1.555025551612633</v>
+        <v>1.56446510297059</v>
       </c>
       <c r="G15">
-        <v>0.001162040051644313</v>
+        <v>0.001151489383497115</v>
       </c>
       <c r="H15">
-        <v>1.048114460662531</v>
+        <v>1.03381418460641</v>
       </c>
       <c r="I15">
-        <v>0.911790745813075</v>
+        <v>0.8834093815248419</v>
       </c>
       <c r="J15">
-        <v>-1.227861026415128</v>
+        <v>-1.208099623809543</v>
       </c>
       <c r="K15">
-        <v>3.250584410275972</v>
+        <v>3.243882876983559</v>
       </c>
     </row>
     <row r="16">
       <c r="A16">
-        <v>0.7</v>
+        <v>0.6</v>
       </c>
       <c r="B16" t="inlineStr">
         <is>
@@ -1415,28 +1415,213 @@
         <v>14</v>
       </c>
       <c r="D16">
+        <v>1.17667267981943</v>
+      </c>
+      <c r="E16">
+        <v>0.5450977852431191</v>
+      </c>
+      <c r="F16">
+        <v>1.808247574395741</v>
+      </c>
+      <c r="G16">
+        <v>0.001442771646569081</v>
+      </c>
+      <c r="H16">
+        <v>1.129769598097096</v>
+      </c>
+      <c r="I16">
+        <v>0.9013060588896876</v>
+      </c>
+      <c r="J16">
+        <v>-1.20793987389064</v>
+      </c>
+      <c r="K16">
+        <v>3.5612852335295</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17">
+        <v>0.6</v>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Excluding absolute cell counts - Tsubakihara et al. (2012)</t>
+        </is>
+      </c>
+      <c r="C17">
+        <v>16</v>
+      </c>
+      <c r="D17">
+        <v>1.081879369758752</v>
+      </c>
+      <c r="E17">
+        <v>0.5291851736037961</v>
+      </c>
+      <c r="F17">
+        <v>1.634573565913708</v>
+      </c>
+      <c r="G17">
+        <v>0.0008175071954126278</v>
+      </c>
+      <c r="H17">
+        <v>1.018136971811179</v>
+      </c>
+      <c r="I17">
+        <v>0.8712955597511479</v>
+      </c>
+      <c r="J17">
+        <v>-1.142090818760193</v>
+      </c>
+      <c r="K17">
+        <v>3.305849558277697</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18">
+        <v>0.7</v>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Main analysis</t>
+        </is>
+      </c>
+      <c r="C18">
+        <v>17</v>
+      </c>
+      <c r="D18">
+        <v>0.9961339727332291</v>
+      </c>
+      <c r="E18">
+        <v>0.4541034330686241</v>
+      </c>
+      <c r="F18">
+        <v>1.538164512397834</v>
+      </c>
+      <c r="G18">
+        <v>0.001284757590773748</v>
+      </c>
+      <c r="H18">
+        <v>1.071724955611667</v>
+      </c>
+      <c r="I18">
+        <v>0.9172857471617978</v>
+      </c>
+      <c r="J18">
+        <v>-1.26675486296762</v>
+      </c>
+      <c r="K18">
+        <v>3.259022808434078</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19">
+        <v>0.7</v>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Lancaster et al. (2005) - n / 3</t>
+        </is>
+      </c>
+      <c r="C19">
+        <v>17</v>
+      </c>
+      <c r="D19">
+        <v>1.011361691930422</v>
+      </c>
+      <c r="E19">
+        <v>0.4676978322482107</v>
+      </c>
+      <c r="F19">
+        <v>1.555025551612633</v>
+      </c>
+      <c r="G19">
+        <v>0.001162040051644313</v>
+      </c>
+      <c r="H19">
+        <v>1.048114460662531</v>
+      </c>
+      <c r="I19">
+        <v>0.911790745813075</v>
+      </c>
+      <c r="J19">
+        <v>-1.227861026415128</v>
+      </c>
+      <c r="K19">
+        <v>3.250584410275972</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20">
+        <v>0.7</v>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>Excluding crossover design - Lancaster et al. (2005)</t>
+        </is>
+      </c>
+      <c r="C20">
+        <v>14</v>
+      </c>
+      <c r="D20">
         <v>1.174136162174575</v>
       </c>
-      <c r="E16">
+      <c r="E20">
         <v>0.5465663207823103</v>
       </c>
-      <c r="F16">
+      <c r="F20">
         <v>1.801706003566839</v>
       </c>
-      <c r="G16">
+      <c r="G20">
         <v>0.001397511424657796</v>
       </c>
-      <c r="H16">
+      <c r="H20">
         <v>1.133557956211395</v>
       </c>
-      <c r="I16">
+      <c r="I20">
         <v>0.9253854438950078</v>
       </c>
-      <c r="J16">
+      <c r="J20">
         <v>-1.212470035434127</v>
       </c>
-      <c r="K16">
+      <c r="K20">
         <v>3.560742359783276</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21">
+        <v>0.7</v>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>Excluding absolute cell counts - Tsubakihara et al. (2012)</t>
+        </is>
+      </c>
+      <c r="C21">
+        <v>16</v>
+      </c>
+      <c r="D21">
+        <v>1.078276179463756</v>
+      </c>
+      <c r="E21">
+        <v>0.5278406577256268</v>
+      </c>
+      <c r="F21">
+        <v>1.628711701201886</v>
+      </c>
+      <c r="G21">
+        <v>0.0008122878371896964</v>
+      </c>
+      <c r="H21">
+        <v>1.026079718582479</v>
+      </c>
+      <c r="I21">
+        <v>0.9030360207597736</v>
+      </c>
+      <c r="J21">
+        <v>-1.15249835375161</v>
+      </c>
+      <c r="K21">
+        <v>3.309050712679122</v>
       </c>
     </row>
   </sheetData>

--- a/downloads/Th1_pre_post_results.xlsx
+++ b/downloads/Th1_pre_post_results.xlsx
@@ -824,7 +824,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:K21"/>
+  <dimension ref="A1:S21"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -883,6 +883,46 @@
           <t>pi_upper</t>
         </is>
       </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>eg_t</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>eg_df</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>eg_p</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>tf_k0</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>tf_side</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
+          <t>tf_g</t>
+        </is>
+      </c>
+      <c r="R1" s="1" t="inlineStr">
+        <is>
+          <t>tf_lo</t>
+        </is>
+      </c>
+      <c r="S1" s="1" t="inlineStr">
+        <is>
+          <t>tf_up</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2">
@@ -920,6 +960,32 @@
       <c r="K2">
         <v>3.206897999439386</v>
       </c>
+      <c r="L2">
+        <v>2.031868283676853</v>
+      </c>
+      <c r="M2">
+        <v>15</v>
+      </c>
+      <c r="N2">
+        <v>0.0602710918009841</v>
+      </c>
+      <c r="O2">
+        <v>1</v>
+      </c>
+      <c r="P2" t="inlineStr">
+        <is>
+          <t>left</t>
+        </is>
+      </c>
+      <c r="Q2">
+        <v>0.8878911172675625</v>
+      </c>
+      <c r="R2">
+        <v>0.321839686736983</v>
+      </c>
+      <c r="S2">
+        <v>1.453942547798142</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3">
@@ -957,6 +1023,32 @@
       <c r="K3">
         <v>3.179584110134805</v>
       </c>
+      <c r="L3">
+        <v>1.201597066689921</v>
+      </c>
+      <c r="M3">
+        <v>15</v>
+      </c>
+      <c r="N3">
+        <v>0.2481484189007287</v>
+      </c>
+      <c r="O3">
+        <v>0</v>
+      </c>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>left</t>
+        </is>
+      </c>
+      <c r="Q3">
+        <v>1.023271935603675</v>
+      </c>
+      <c r="R3">
+        <v>0.5028961564380842</v>
+      </c>
+      <c r="S3">
+        <v>1.543647714769266</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4">
@@ -994,6 +1086,32 @@
       <c r="K4">
         <v>3.517211133647821</v>
       </c>
+      <c r="L4">
+        <v>2.143578377046663</v>
+      </c>
+      <c r="M4">
+        <v>12</v>
+      </c>
+      <c r="N4">
+        <v>0.05325007356702324</v>
+      </c>
+      <c r="O4">
+        <v>0</v>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>left</t>
+        </is>
+      </c>
+      <c r="Q4">
+        <v>1.17078499222204</v>
+      </c>
+      <c r="R4">
+        <v>0.5775874960825993</v>
+      </c>
+      <c r="S4">
+        <v>1.763982488361481</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5">
@@ -1031,6 +1149,32 @@
       <c r="K5">
         <v>3.254681632997313</v>
       </c>
+      <c r="L5">
+        <v>1.420728685159549</v>
+      </c>
+      <c r="M5">
+        <v>14</v>
+      </c>
+      <c r="N5">
+        <v>0.1772840390050412</v>
+      </c>
+      <c r="O5">
+        <v>0</v>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>left</t>
+        </is>
+      </c>
+      <c r="Q5">
+        <v>1.079473259512304</v>
+      </c>
+      <c r="R5">
+        <v>0.5509612744887066</v>
+      </c>
+      <c r="S5">
+        <v>1.607985244535902</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6">
@@ -1068,6 +1212,32 @@
       <c r="K6">
         <v>3.227765046487138</v>
       </c>
+      <c r="L6">
+        <v>2.064735218479439</v>
+      </c>
+      <c r="M6">
+        <v>15</v>
+      </c>
+      <c r="N6">
+        <v>0.05668483362521697</v>
+      </c>
+      <c r="O6">
+        <v>1</v>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>left</t>
+        </is>
+      </c>
+      <c r="Q6">
+        <v>0.886808613356261</v>
+      </c>
+      <c r="R6">
+        <v>0.3223349987978888</v>
+      </c>
+      <c r="S6">
+        <v>1.451282227914633</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7">
@@ -1105,6 +1275,32 @@
       <c r="K7">
         <v>3.205919414683784</v>
       </c>
+      <c r="L7">
+        <v>1.225241360168628</v>
+      </c>
+      <c r="M7">
+        <v>15</v>
+      </c>
+      <c r="N7">
+        <v>0.2393760391052964</v>
+      </c>
+      <c r="O7">
+        <v>0</v>
+      </c>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>left</t>
+        </is>
+      </c>
+      <c r="Q7">
+        <v>1.02279115442236</v>
+      </c>
+      <c r="R7">
+        <v>0.5037535903433934</v>
+      </c>
+      <c r="S7">
+        <v>1.541828718501327</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8">
@@ -1142,6 +1338,32 @@
       <c r="K8">
         <v>3.536875835138552</v>
       </c>
+      <c r="L8">
+        <v>2.184944218722586</v>
+      </c>
+      <c r="M8">
+        <v>12</v>
+      </c>
+      <c r="N8">
+        <v>0.04945391503623476</v>
+      </c>
+      <c r="O8">
+        <v>0</v>
+      </c>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>left</t>
+        </is>
+      </c>
+      <c r="Q8">
+        <v>1.173903014580307</v>
+      </c>
+      <c r="R8">
+        <v>0.5830728490893834</v>
+      </c>
+      <c r="S8">
+        <v>1.76473318007123</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9">
@@ -1179,6 +1401,32 @@
       <c r="K9">
         <v>3.27624165263383</v>
       </c>
+      <c r="L9">
+        <v>1.461109524598232</v>
+      </c>
+      <c r="M9">
+        <v>14</v>
+      </c>
+      <c r="N9">
+        <v>0.1660645086699716</v>
+      </c>
+      <c r="O9">
+        <v>0</v>
+      </c>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>left</t>
+        </is>
+      </c>
+      <c r="Q9">
+        <v>1.08139023472814</v>
+      </c>
+      <c r="R9">
+        <v>0.5547653125218472</v>
+      </c>
+      <c r="S9">
+        <v>1.608015156934433</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10">
@@ -1216,6 +1464,32 @@
       <c r="K10">
         <v>3.244805225706148</v>
       </c>
+      <c r="L10">
+        <v>2.107956836971503</v>
+      </c>
+      <c r="M10">
+        <v>15</v>
+      </c>
+      <c r="N10">
+        <v>0.05226642538781255</v>
+      </c>
+      <c r="O10">
+        <v>0</v>
+      </c>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>left</t>
+        </is>
+      </c>
+      <c r="Q10">
+        <v>0.9979875900570733</v>
+      </c>
+      <c r="R10">
+        <v>0.4800377634953926</v>
+      </c>
+      <c r="S10">
+        <v>1.515937416618754</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11">
@@ -1253,6 +1527,32 @@
       <c r="K11">
         <v>3.227931272788303</v>
       </c>
+      <c r="L11">
+        <v>1.256241286946693</v>
+      </c>
+      <c r="M11">
+        <v>15</v>
+      </c>
+      <c r="N11">
+        <v>0.2282422484640021</v>
+      </c>
+      <c r="O11">
+        <v>0</v>
+      </c>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>left</t>
+        </is>
+      </c>
+      <c r="Q11">
+        <v>1.021224129395345</v>
+      </c>
+      <c r="R11">
+        <v>0.5042310802016556</v>
+      </c>
+      <c r="S11">
+        <v>1.538217178589034</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12">
@@ -1290,6 +1590,32 @@
       <c r="K12">
         <v>3.552199396402144</v>
       </c>
+      <c r="L12">
+        <v>2.239749869886758</v>
+      </c>
+      <c r="M12">
+        <v>12</v>
+      </c>
+      <c r="N12">
+        <v>0.04481726095292035</v>
+      </c>
+      <c r="O12">
+        <v>0</v>
+      </c>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>left</t>
+        </is>
+      </c>
+      <c r="Q12">
+        <v>1.176097424251494</v>
+      </c>
+      <c r="R12">
+        <v>0.5884358169334069</v>
+      </c>
+      <c r="S12">
+        <v>1.763759031569581</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13">
@@ -1327,6 +1653,32 @@
       <c r="K13">
         <v>3.293873329018589</v>
       </c>
+      <c r="L13">
+        <v>1.514059510847974</v>
+      </c>
+      <c r="M13">
+        <v>14</v>
+      </c>
+      <c r="N13">
+        <v>0.1522567682864528</v>
+      </c>
+      <c r="O13">
+        <v>0</v>
+      </c>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>left</t>
+        </is>
+      </c>
+      <c r="Q13">
+        <v>1.082423693418966</v>
+      </c>
+      <c r="R13">
+        <v>0.5583457164127124</v>
+      </c>
+      <c r="S13">
+        <v>1.60650167042522</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14">
@@ -1364,6 +1716,32 @@
       <c r="K14">
         <v>3.256283693243018</v>
       </c>
+      <c r="L14">
+        <v>2.167366645943178</v>
+      </c>
+      <c r="M14">
+        <v>15</v>
+      </c>
+      <c r="N14">
+        <v>0.04670984728358762</v>
+      </c>
+      <c r="O14">
+        <v>0</v>
+      </c>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>left</t>
+        </is>
+      </c>
+      <c r="Q14">
+        <v>0.9985041158865274</v>
+      </c>
+      <c r="R14">
+        <v>0.4838701844724027</v>
+      </c>
+      <c r="S14">
+        <v>1.513138047300652</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15">
@@ -1401,6 +1779,32 @@
       <c r="K15">
         <v>3.243882876983559</v>
       </c>
+      <c r="L15">
+        <v>1.298646224181029</v>
+      </c>
+      <c r="M15">
+        <v>15</v>
+      </c>
+      <c r="N15">
+        <v>0.2136759055286967</v>
+      </c>
+      <c r="O15">
+        <v>0</v>
+      </c>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>left</t>
+        </is>
+      </c>
+      <c r="Q15">
+        <v>1.017891626587008</v>
+      </c>
+      <c r="R15">
+        <v>0.5038888690859271</v>
+      </c>
+      <c r="S15">
+        <v>1.531894384088089</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16">
@@ -1438,6 +1842,32 @@
       <c r="K16">
         <v>3.5612852335295</v>
       </c>
+      <c r="L16">
+        <v>2.315877790958315</v>
+      </c>
+      <c r="M16">
+        <v>12</v>
+      </c>
+      <c r="N16">
+        <v>0.03905798180620475</v>
+      </c>
+      <c r="O16">
+        <v>0</v>
+      </c>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>left</t>
+        </is>
+      </c>
+      <c r="Q16">
+        <v>1.176672679819431</v>
+      </c>
+      <c r="R16">
+        <v>0.5932666882823168</v>
+      </c>
+      <c r="S16">
+        <v>1.760078671356545</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17">
@@ -1475,6 +1905,32 @@
       <c r="K17">
         <v>3.305849558277697</v>
       </c>
+      <c r="L17">
+        <v>1.58658555034743</v>
+      </c>
+      <c r="M17">
+        <v>14</v>
+      </c>
+      <c r="N17">
+        <v>0.1349286504466718</v>
+      </c>
+      <c r="O17">
+        <v>0</v>
+      </c>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>left</t>
+        </is>
+      </c>
+      <c r="Q17">
+        <v>1.081879369758752</v>
+      </c>
+      <c r="R17">
+        <v>0.5612441960472349</v>
+      </c>
+      <c r="S17">
+        <v>1.60251454347027</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18">
@@ -1512,6 +1968,32 @@
       <c r="K18">
         <v>3.259022808434078</v>
       </c>
+      <c r="L18">
+        <v>2.254221607808107</v>
+      </c>
+      <c r="M18">
+        <v>15</v>
+      </c>
+      <c r="N18">
+        <v>0.03956575871628636</v>
+      </c>
+      <c r="O18">
+        <v>0</v>
+      </c>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>left</t>
+        </is>
+      </c>
+      <c r="Q18">
+        <v>0.9961339727332291</v>
+      </c>
+      <c r="R18">
+        <v>0.4860895730188416</v>
+      </c>
+      <c r="S18">
+        <v>1.506178372447617</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19">
@@ -1549,6 +2031,32 @@
       <c r="K19">
         <v>3.250584410275972</v>
       </c>
+      <c r="L19">
+        <v>1.360143356527817</v>
+      </c>
+      <c r="M19">
+        <v>15</v>
+      </c>
+      <c r="N19">
+        <v>0.19387670968349</v>
+      </c>
+      <c r="O19">
+        <v>0</v>
+      </c>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>left</t>
+        </is>
+      </c>
+      <c r="Q19">
+        <v>1.011361691930422</v>
+      </c>
+      <c r="R19">
+        <v>0.5016877833561407</v>
+      </c>
+      <c r="S19">
+        <v>1.521035600504703</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20">
@@ -1586,6 +2094,32 @@
       <c r="K20">
         <v>3.560742359783276</v>
       </c>
+      <c r="L20">
+        <v>2.428966099513578</v>
+      </c>
+      <c r="M20">
+        <v>12</v>
+      </c>
+      <c r="N20">
+        <v>0.03179252107440306</v>
+      </c>
+      <c r="O20">
+        <v>0</v>
+      </c>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>left</t>
+        </is>
+      </c>
+      <c r="Q20">
+        <v>1.174136162174574</v>
+      </c>
+      <c r="R20">
+        <v>0.5965213001522898</v>
+      </c>
+      <c r="S20">
+        <v>1.751751024196857</v>
+      </c>
     </row>
     <row r="21">
       <c r="A21">
@@ -1622,6 +2156,32 @@
       </c>
       <c r="K21">
         <v>3.309050712679122</v>
+      </c>
+      <c r="L21">
+        <v>1.69217724094642</v>
+      </c>
+      <c r="M21">
+        <v>14</v>
+      </c>
+      <c r="N21">
+        <v>0.1127391368718473</v>
+      </c>
+      <c r="O21">
+        <v>0</v>
+      </c>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>left</t>
+        </is>
+      </c>
+      <c r="Q21">
+        <v>1.078276179463756</v>
+      </c>
+      <c r="R21">
+        <v>0.56235017856956</v>
+      </c>
+      <c r="S21">
+        <v>1.594202180357953</v>
       </c>
     </row>
   </sheetData>
